--- a/assets/libreoffice_calc_njc/8bae8f17-fe56-49ef-a561-f9761e9c72a6/Inventory_L2_03.xlsx
+++ b/assets/libreoffice_calc_njc/8bae8f17-fe56-49ef-a561-f9761e9c72a6/Inventory_L2_03.xlsx
@@ -247,12 +247,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -274,9 +278,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -303,406 +307,406 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="2" t="n">
         <v>899.99</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="2" t="n">
         <f aca="false">D2*E2</f>
         <v>40499.55</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="2" t="n">
         <v>24.99</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="2" t="n">
         <f aca="false">D3*E3</f>
         <v>4998</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="2" t="n">
         <v>39.99</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="2" t="n">
         <f aca="false">D4*E4</f>
         <v>5998.5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="2" t="n">
         <v>449.99</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="2" t="n">
         <f aca="false">D5*E5</f>
         <v>13499.7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="2" t="n">
         <v>79.99</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="2" t="n">
         <f aca="false">D6*E6</f>
         <v>14398.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="2" t="n">
         <v>69.99</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="2" t="n">
         <f aca="false">D7*E7</f>
         <v>6299.1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="2" t="n">
         <v>149.99</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="2" t="n">
         <f aca="false">D8*E8</f>
         <v>17998.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="2" t="n">
         <v>34.99</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="2" t="n">
         <f aca="false">D9*E9</f>
         <v>2624.25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="2" t="n">
         <v>12.99</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="2" t="n">
         <f aca="false">D10*E10</f>
         <v>3897</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="2" t="n">
         <v>599.99</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="2" t="n">
         <f aca="false">D11*E11</f>
         <v>14999.75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="2" t="n">
         <v>89.99</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="2" t="n">
         <f aca="false">D12*E12</f>
         <v>5399.4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="2" t="n">
         <v>14.99</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="2" t="n">
         <f aca="false">D13*E13</f>
         <v>3747.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="2" t="n">
         <v>29.99</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="2" t="n">
         <f aca="false">D14*E14</f>
         <v>4798.4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="2" t="n">
         <v>59.99</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="2" t="n">
         <f aca="false">D15*E15</f>
         <v>2399.6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="2" t="n">
         <v>49.99</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="2" t="n">
         <f aca="false">D16*E16</f>
         <v>4999</v>
       </c>
